--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -20,7 +20,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="8">
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>/explore</t>
+  </si>
+  <si>
+    <t>/features</t>
+  </si>
+  <si>
+    <t>/features/otc-desk</t>
+  </si>
+  <si>
+    <t>/company</t>
+  </si>
+  <si>
+    <t>/support</t>
+  </si>
+  <si>
+    <t>/blog</t>
+  </si>
+  <si>
+    <t>Blog and news</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -623,10 +648,8 @@
           <t>Explore</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr" s="0">
-        <is>
-          <t>https://mb.io/en-AE/explore</t>
-        </is>
+      <c r="B2" t="s" s="0">
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr" s="0">
         <is>
@@ -640,10 +663,8 @@
           <t>Features</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr" s="0">
-        <is>
-          <t>https://mb.io/en-AE/features</t>
-        </is>
+      <c r="B3" t="s" s="0">
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr" s="0">
         <is>
@@ -657,10 +678,8 @@
           <t>OTC Desk</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr" s="0">
-        <is>
-          <t>https://mb.io/en-AE/features/otc-desk</t>
-        </is>
+      <c r="B4" t="s" s="0">
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr" s="0">
         <is>
@@ -674,10 +693,8 @@
           <t>Company</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr" s="0">
-        <is>
-          <t>https://mb.io/en-AE/company</t>
-        </is>
+      <c r="B5" t="s" s="0">
+        <v>4</v>
       </c>
       <c r="C5" t="inlineStr" s="0">
         <is>
@@ -691,10 +708,8 @@
           <t>Support</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr" s="0">
-        <is>
-          <t>https://mb.io/en-AE/support</t>
-        </is>
+      <c r="B6" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="C6" t="inlineStr" s="0">
         <is>
@@ -708,16 +723,11 @@
           <t>Blog</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr" s="0">
-        <is>
-          <t>https://mb.io/en-AE/blog</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr" s="0">
-        <v>Blog and news</v>
-        <is>
-          <t>Blog and News</t>
-        </is>
+      <c r="B7" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
